--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.20887116945198</v>
+        <v>3.771441565035947</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6506125485769</v>
+        <v>3.843224539143746</v>
       </c>
       <c r="E2" t="n">
-        <v>7.165210826543964</v>
+        <v>1.164346759313394</v>
       </c>
       <c r="F2" t="n">
-        <v>7.384241772907363</v>
+        <v>1.199939288097447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.35397896349235</v>
+        <v>1.032521581567507</v>
       </c>
       <c r="D3" t="n">
-        <v>6.35397896349235</v>
+        <v>1.032521581567507</v>
       </c>
       <c r="E3" t="n">
-        <v>7.165210826543964</v>
+        <v>1.164346759313394</v>
       </c>
       <c r="F3" t="n">
-        <v>7.384241772907363</v>
+        <v>1.199939288097447</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.54284459728041</v>
+        <v>1.713212247058067</v>
       </c>
       <c r="D4" t="n">
-        <v>10.42065091047214</v>
+        <v>1.693355772951723</v>
       </c>
       <c r="E4" t="n">
-        <v>7.165210826543964</v>
+        <v>1.164346759313394</v>
       </c>
       <c r="F4" t="n">
-        <v>7.384241772907363</v>
+        <v>1.199939288097447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
